--- a/unit_commitment.xlsx
+++ b/unit_commitment.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\GitHub\energylab-emw-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5540D030-B39D-4B40-BC6B-ABB4DBF15EA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D2631D1-FAD7-4EEE-A88C-A4C78EA360EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="420" xr2:uid="{C4103D47-9B4C-4342-BFC4-2639338CB718}"/>
   </bookViews>
@@ -1450,7 +1450,7 @@
         <v>5</v>
       </c>
       <c r="C2" s="4"/>
-      <c r="D2" s="4">
+      <c r="D2" s="18">
         <v>75</v>
       </c>
       <c r="E2" s="4">
@@ -1469,7 +1469,7 @@
         <v>7</v>
       </c>
       <c r="C3" s="6"/>
-      <c r="D3" s="6">
+      <c r="D3" s="17">
         <v>0</v>
       </c>
       <c r="E3" s="6">
@@ -1487,10 +1487,10 @@
       <c r="B4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="17">
         <v>1</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="17">
         <v>175</v>
       </c>
       <c r="E4" s="8">
@@ -1508,10 +1508,10 @@
       <c r="B5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="6">
-        <v>0</v>
-      </c>
-      <c r="D5" s="6">
+      <c r="C5" s="17">
+        <v>0</v>
+      </c>
+      <c r="D5" s="17">
         <v>0</v>
       </c>
       <c r="E5" s="6">
